--- a/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-vaccination-document.xlsx
+++ b/htr-corps-ressources-FHIR/ig/StructureDefinition-fr-vaccination-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$139</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4750" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5114" uniqueCount="659">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-01T13:19:09+00:00</t>
+    <t>2025-09-02T15:19:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1484,13 +1484,31 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
   </si>
   <si>
+    <t>Immunization.performer.actor.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
     <t>Immunization.performer.actor.extension:author.extension:reference</t>
   </si>
   <si>
     <t>reference</t>
-  </si>
-  <si>
-    <t>Référence vers le rôle du praticien dans le document</t>
   </si>
   <si>
     <t>Immunization.performer.actor.extension:author.extension:reference.id</t>
@@ -1559,6 +1577,21 @@
   </si>
   <si>
     <t>PRF</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:executant.extension:typeCode</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:executant.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:executant.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:executant.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Immunization.performer.actor.extension:executant.extension:typeCode.value[x]</t>
   </si>
   <si>
     <t>Immunization.performer.actor.extension:executant.extension:reference</t>
@@ -2334,7 +2367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO129"/>
+  <dimension ref="A1:AO139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="65.734375" customWidth="true" bestFit="true"/>
@@ -10643,7 +10676,7 @@
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s" s="2">
         <v>89</v>
@@ -11120,7 +11153,7 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>481</v>
+        <v>190</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>239</v>
@@ -11209,12 +11242,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C77" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="B77" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11235,24 +11270,22 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q77" s="2"/>
       <c r="R77" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="S77" t="s" s="2">
         <v>78</v>
@@ -11294,19 +11327,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11315,7 +11348,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11326,10 +11359,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11340,7 +11373,7 @@
         <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11352,13 +11385,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>487</v>
+        <v>210</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11409,7 +11442,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11421,7 +11454,7 @@
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11430,7 +11463,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11441,14 +11474,12 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>489</v>
-      </c>
+        <v>467</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11457,7 +11488,7 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11469,13 +11500,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>455</v>
+        <v>135</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>490</v>
+        <v>229</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>457</v>
+        <v>137</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11514,16 +11545,16 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF79" t="s" s="2">
         <v>219</v>
@@ -11558,10 +11589,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11569,7 +11600,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>89</v>
@@ -11584,22 +11615,24 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>78</v>
@@ -11641,10 +11674,10 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>89</v>
@@ -11662,7 +11695,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11673,10 +11706,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11684,10 +11717,10 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>78</v>
@@ -11699,13 +11732,13 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>135</v>
+        <v>487</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>137</v>
+        <v>240</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11744,31 +11777,31 @@
         <v>78</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -11777,7 +11810,7 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -11788,14 +11821,12 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>78</v>
       </c>
@@ -11816,22 +11847,24 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>78</v>
@@ -11873,19 +11906,19 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11894,7 +11927,7 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -11905,10 +11938,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11919,7 +11952,7 @@
         <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11931,13 +11964,13 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>210</v>
+        <v>493</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>211</v>
+        <v>239</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>212</v>
+        <v>240</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11988,7 +12021,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12000,7 +12033,7 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12009,7 +12042,7 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12020,12 +12053,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="B84" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12034,7 +12069,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12046,13 +12081,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>135</v>
+        <v>455</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>229</v>
+        <v>496</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12091,16 +12126,16 @@
         <v>78</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
         <v>219</v>
@@ -12135,10 +12170,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12146,7 +12181,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>89</v>
@@ -12161,24 +12196,22 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q85" s="2"/>
       <c r="R85" t="s" s="2">
-        <v>463</v>
+        <v>78</v>
       </c>
       <c r="S85" t="s" s="2">
         <v>78</v>
@@ -12220,10 +12253,10 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="AG85" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
         <v>89</v>
@@ -12241,7 +12274,7 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12252,10 +12285,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12263,10 +12296,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12278,13 +12311,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12293,7 +12326,7 @@
       </c>
       <c r="Q86" s="2"/>
       <c r="R86" t="s" s="2">
-        <v>498</v>
+        <v>78</v>
       </c>
       <c r="S86" t="s" s="2">
         <v>78</v>
@@ -12311,41 +12344,43 @@
         <v>78</v>
       </c>
       <c r="X86" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y86" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z86" t="s" s="2">
-        <v>473</v>
+        <v>78</v>
       </c>
       <c r="AA86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12354,7 +12389,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12371,7 +12406,7 @@
         <v>461</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
@@ -12396,7 +12431,7 @@
         <v>135</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>476</v>
+        <v>229</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>137</v>
@@ -12755,7 +12790,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>78</v>
@@ -12855,7 +12890,7 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>481</v>
+        <v>109</v>
       </c>
       <c r="L91" t="s" s="2">
         <v>239</v>
@@ -12870,7 +12905,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>78</v>
@@ -12888,13 +12923,11 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>78</v>
+        <v>473</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12944,18 +12977,20 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>89</v>
@@ -12970,24 +13005,22 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>232</v>
+        <v>476</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>78</v>
@@ -13029,19 +13062,19 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
@@ -13050,7 +13083,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13061,10 +13094,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13075,7 +13108,7 @@
         <v>79</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>78</v>
@@ -13087,13 +13120,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>487</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13144,7 +13177,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13156,7 +13189,7 @@
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13165,7 +13198,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13176,10 +13209,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>506</v>
+        <v>467</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13190,7 +13223,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13199,20 +13232,18 @@
         <v>78</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>507</v>
+        <v>229</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N94" s="2"/>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13249,31 +13280,31 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>510</v>
+        <v>219</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>511</v>
+        <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13282,7 +13313,7 @@
         <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13293,10 +13324,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13304,7 +13335,7 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G95" t="s" s="2">
         <v>89</v>
@@ -13316,19 +13347,19 @@
         <v>78</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>513</v>
+        <v>232</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>514</v>
+        <v>233</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>515</v>
+        <v>234</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13336,7 +13367,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>78</v>
@@ -13354,13 +13385,13 @@
         <v>78</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>516</v>
+        <v>78</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>517</v>
+        <v>78</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>78</v>
@@ -13378,10 +13409,10 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>518</v>
+        <v>236</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH95" t="s" s="2">
         <v>89</v>
@@ -13390,7 +13421,7 @@
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13410,10 +13441,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>519</v>
+        <v>471</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13433,20 +13464,18 @@
         <v>78</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>171</v>
+        <v>190</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>520</v>
+        <v>239</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>522</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
@@ -13495,7 +13524,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>523</v>
+        <v>241</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13516,7 +13545,7 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>524</v>
+        <v>132</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>78</v>
@@ -13527,18 +13556,20 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>89</v>
@@ -13550,20 +13581,18 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>526</v>
+        <v>229</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>528</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -13612,19 +13641,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>529</v>
+        <v>219</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -13633,7 +13662,7 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13644,10 +13673,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>530</v>
+        <v>465</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13661,22 +13690,22 @@
         <v>89</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>531</v>
+        <v>210</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>532</v>
+        <v>211</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>533</v>
+        <v>212</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13727,28 +13756,28 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>530</v>
+        <v>213</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>536</v>
+        <v>214</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13759,10 +13788,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>537</v>
+        <v>512</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>537</v>
+        <v>467</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13773,7 +13802,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13785,13 +13814,13 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>538</v>
+        <v>229</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>539</v>
+        <v>137</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13818,31 +13847,31 @@
         <v>78</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>540</v>
+        <v>78</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>541</v>
+        <v>78</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>537</v>
+        <v>219</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13854,16 +13883,16 @@
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>542</v>
+        <v>78</v>
       </c>
       <c r="AL99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>543</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13874,10 +13903,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>544</v>
+        <v>513</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>544</v>
+        <v>469</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13885,13 +13914,13 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>78</v>
@@ -13900,22 +13929,24 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>545</v>
+        <v>103</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>546</v>
+        <v>232</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>78</v>
@@ -13957,22 +13988,22 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>544</v>
+        <v>236</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>548</v>
+        <v>78</v>
       </c>
       <c r="AL100" t="s" s="2">
         <v>78</v>
@@ -13989,10 +14020,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>549</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>549</v>
+        <v>471</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14009,30 +14040,26 @@
         <v>78</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>296</v>
+        <v>487</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>550</v>
+        <v>239</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q101" t="s" s="2">
-        <v>553</v>
-      </c>
+      <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
         <v>78</v>
       </c>
@@ -14076,7 +14103,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>549</v>
+        <v>241</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14094,7 +14121,7 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>554</v>
+        <v>78</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>132</v>
@@ -14108,10 +14135,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>555</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>555</v>
+        <v>489</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14119,10 +14146,10 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>78</v>
@@ -14134,22 +14161,24 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>556</v>
+        <v>232</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>78</v>
@@ -14167,13 +14196,13 @@
         <v>78</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>78</v>
@@ -14191,19 +14220,19 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>555</v>
+        <v>236</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14223,10 +14252,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>560</v>
+        <v>516</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>560</v>
+        <v>492</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14237,7 +14266,7 @@
         <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14249,13 +14278,13 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>422</v>
+        <v>493</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>561</v>
+        <v>239</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>562</v>
+        <v>240</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14306,19 +14335,19 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>560</v>
+        <v>241</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>563</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -14338,10 +14367,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>564</v>
+        <v>517</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14361,18 +14390,20 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>210</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>211</v>
+        <v>518</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14421,7 +14452,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>213</v>
+        <v>521</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14430,10 +14461,10 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
@@ -14442,7 +14473,7 @@
         <v>78</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>78</v>
@@ -14453,21 +14484,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>565</v>
+        <v>523</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>78</v>
@@ -14476,19 +14507,19 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>216</v>
+        <v>524</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>217</v>
+        <v>525</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>167</v>
+        <v>526</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14514,13 +14545,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>78</v>
+        <v>528</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -14538,19 +14569,19 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>219</v>
+        <v>529</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>78</v>
@@ -14559,7 +14590,7 @@
         <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>78</v>
@@ -14570,46 +14601,44 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J106" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>432</v>
+        <v>531</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>433</v>
+        <v>532</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>78</v>
       </c>
@@ -14657,19 +14686,19 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>434</v>
+        <v>534</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
@@ -14678,7 +14707,7 @@
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>132</v>
+        <v>535</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14689,10 +14718,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>567</v>
+        <v>536</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14712,18 +14741,20 @@
         <v>78</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
         <v>210</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>568</v>
+        <v>537</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -14772,7 +14803,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>567</v>
+        <v>540</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14790,7 +14821,7 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>570</v>
+        <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>132</v>
@@ -14804,10 +14835,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14821,22 +14852,22 @@
         <v>89</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>103</v>
+        <v>542</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>572</v>
+        <v>543</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>573</v>
+        <v>544</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14887,13 +14918,13 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>571</v>
+        <v>541</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>78</v>
@@ -14902,13 +14933,13 @@
         <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>132</v>
+        <v>547</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14919,10 +14950,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14933,7 +14964,7 @@
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>78</v>
@@ -14945,13 +14976,13 @@
         <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>332</v>
+        <v>190</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>576</v>
+        <v>550</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -14978,13 +15009,13 @@
         <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>78</v>
+        <v>552</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15002,13 +15033,13 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>78</v>
@@ -15017,13 +15048,13 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>78</v>
+        <v>553</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>577</v>
+        <v>78</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>132</v>
+        <v>554</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -15034,10 +15065,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15048,10 +15079,10 @@
         <v>79</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
@@ -15060,13 +15091,13 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>332</v>
+        <v>556</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15117,13 +15148,13 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>578</v>
+        <v>555</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>78</v>
@@ -15132,10 +15163,10 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>581</v>
+        <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>132</v>
@@ -15149,10 +15180,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15163,32 +15194,36 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>562</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="R111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15208,13 +15243,13 @@
         <v>78</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>586</v>
+        <v>78</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>78</v>
@@ -15232,13 +15267,13 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
@@ -15250,7 +15285,7 @@
         <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>132</v>
@@ -15264,10 +15299,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15278,7 +15313,7 @@
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>78</v>
@@ -15293,10 +15328,10 @@
         <v>190</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15326,10 +15361,10 @@
         <v>194</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15347,13 +15382,13 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>78</v>
@@ -15379,10 +15414,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15408,14 +15443,12 @@
         <v>422</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>78</v>
@@ -15464,7 +15497,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15476,16 +15509,16 @@
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>574</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>597</v>
+        <v>78</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>598</v>
+        <v>132</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>78</v>
@@ -15496,10 +15529,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15611,10 +15644,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>600</v>
+        <v>576</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15728,10 +15761,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>601</v>
+        <v>577</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15847,10 +15880,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15873,13 +15906,13 @@
         <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>332</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>603</v>
+        <v>579</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>604</v>
+        <v>580</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -15930,7 +15963,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>602</v>
+        <v>578</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15948,10 +15981,10 @@
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>605</v>
+        <v>581</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>338</v>
+        <v>132</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>78</v>
@@ -15962,10 +15995,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15988,13 +16021,13 @@
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>607</v>
+        <v>103</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>608</v>
+        <v>583</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16045,7 +16078,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>606</v>
+        <v>582</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -16063,10 +16096,10 @@
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>610</v>
+        <v>78</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>611</v>
+        <v>132</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>78</v>
@@ -16077,10 +16110,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16103,13 +16136,13 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>614</v>
+        <v>587</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16160,7 +16193,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16178,10 +16211,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>615</v>
+        <v>588</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>616</v>
+        <v>132</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16192,10 +16225,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16206,10 +16239,10 @@
         <v>79</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>78</v>
@@ -16218,13 +16251,13 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>422</v>
+        <v>332</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>619</v>
+        <v>591</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -16275,13 +16308,13 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>78</v>
@@ -16293,7 +16326,7 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>78</v>
+        <v>592</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>132</v>
@@ -16307,10 +16340,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>620</v>
+        <v>593</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16321,7 +16354,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>78</v>
@@ -16333,13 +16366,13 @@
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>211</v>
+        <v>594</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>212</v>
+        <v>595</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -16366,13 +16399,13 @@
         <v>78</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>78</v>
+        <v>597</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>78</v>
@@ -16390,28 +16423,28 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>213</v>
+        <v>593</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK121" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -16422,21 +16455,21 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>78</v>
@@ -16448,17 +16481,15 @@
         <v>78</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>216</v>
+        <v>600</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>167</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -16483,13 +16514,13 @@
         <v>78</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>78</v>
+        <v>602</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>78</v>
+        <v>603</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>78</v>
@@ -16507,19 +16538,19 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>219</v>
+        <v>599</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK122" t="s" s="2">
         <v>78</v>
@@ -16528,7 +16559,7 @@
         <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -16539,14 +16570,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>431</v>
+        <v>78</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -16559,26 +16590,24 @@
         <v>78</v>
       </c>
       <c r="I123" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J123" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>135</v>
+        <v>422</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>432</v>
+        <v>605</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>433</v>
+        <v>606</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>78</v>
       </c>
@@ -16626,7 +16655,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>434</v>
+        <v>604</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -16638,16 +16667,16 @@
         <v>78</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>78</v>
+        <v>608</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>132</v>
+        <v>609</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -16658,10 +16687,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>623</v>
+        <v>610</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16687,10 +16716,10 @@
         <v>210</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>624</v>
+        <v>211</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>625</v>
+        <v>212</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16741,7 +16770,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>623</v>
+        <v>213</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -16753,7 +16782,7 @@
         <v>78</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>78</v>
@@ -16762,7 +16791,7 @@
         <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -16773,21 +16802,21 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>78</v>
@@ -16799,15 +16828,17 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>383</v>
+        <v>135</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>627</v>
+        <v>216</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16856,19 +16887,19 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>626</v>
+        <v>219</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>78</v>
@@ -16877,7 +16908,7 @@
         <v>78</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>78</v>
@@ -16888,14 +16919,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>78</v>
+        <v>431</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -16908,22 +16939,26 @@
         <v>78</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>630</v>
+        <v>432</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O126" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
       </c>
@@ -16947,13 +16982,13 @@
         <v>78</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>632</v>
+        <v>78</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>633</v>
+        <v>78</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>78</v>
@@ -16971,7 +17006,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>629</v>
+        <v>434</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16983,7 +17018,7 @@
         <v>78</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>78</v>
@@ -17003,10 +17038,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17014,7 +17049,7 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>89</v>
@@ -17029,17 +17064,15 @@
         <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>635</v>
+        <v>332</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -17076,20 +17109,22 @@
         <v>78</v>
       </c>
       <c r="AB127" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AC127" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE127" t="s" s="2">
-        <v>640</v>
+        <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="AG127" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
         <v>89</v>
@@ -17104,10 +17139,10 @@
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>78</v>
+        <v>616</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>78</v>
@@ -17118,20 +17153,18 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>641</v>
+        <v>617</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="C128" t="s" s="2">
-        <v>642</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>89</v>
@@ -17146,17 +17179,15 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>643</v>
+        <v>619</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17205,10 +17236,10 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>89</v>
@@ -17223,10 +17254,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>78</v>
+        <v>621</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>132</v>
+        <v>622</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -17237,10 +17268,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17263,17 +17294,15 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>645</v>
+        <v>296</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>646</v>
+        <v>624</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="N129" s="2"/>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>78</v>
@@ -17322,7 +17351,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17340,20 +17369,1182 @@
         <v>78</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>78</v>
+        <v>626</v>
       </c>
       <c r="AM129" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO129" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM130" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AN129" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO129" t="s" s="2">
+      <c r="AN130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO130" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO131" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO132" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="133" hidden="true">
+      <c r="A133" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C133" s="2"/>
+      <c r="D133" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="E133" s="2"/>
+      <c r="F133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="J133" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K133" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L133" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M133" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="O133" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="P133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q133" s="2"/>
+      <c r="R133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF133" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AG133" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH133" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ133" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM133" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN133" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO133" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="134" hidden="true">
+      <c r="A134" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="C134" s="2"/>
+      <c r="D134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E134" s="2"/>
+      <c r="F134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K134" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L134" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M134" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q134" s="2"/>
+      <c r="R134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF134" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AG134" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH134" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ134" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM134" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN134" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO134" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="135" hidden="true">
+      <c r="A135" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="D135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E135" s="2"/>
+      <c r="F135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K135" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="L135" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M135" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q135" s="2"/>
+      <c r="R135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF135" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AG135" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH135" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ135" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM135" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN135" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO135" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="136" hidden="true">
+      <c r="A136" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="C136" s="2"/>
+      <c r="D136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E136" s="2"/>
+      <c r="F136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K136" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L136" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M136" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q136" s="2"/>
+      <c r="R136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X136" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Y136" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="Z136" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AA136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF136" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AG136" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH136" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ136" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM136" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN136" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO136" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="137" hidden="true">
+      <c r="A137" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="B137" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="D137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E137" s="2"/>
+      <c r="F137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K137" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="M137" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O137" s="2"/>
+      <c r="P137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q137" s="2"/>
+      <c r="R137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB137" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AC137" s="2"/>
+      <c r="AD137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE137" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AF137" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH137" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ137" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM137" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN137" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO137" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="138" hidden="true">
+      <c r="A138" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="B138" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="D138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E138" s="2"/>
+      <c r="F138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M138" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O138" s="2"/>
+      <c r="P138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q138" s="2"/>
+      <c r="R138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF138" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AG138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH138" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ138" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM138" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN138" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO138" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="139" hidden="true">
+      <c r="A139" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM139" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN139" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO139" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO129">
+  <autoFilter ref="A1:AO139">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17363,7 +18554,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI128">
+  <conditionalFormatting sqref="A2:AI138">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
